--- a/diseases/d030/2026-2029.xlsx
+++ b/diseases/d030/2026-2029.xlsx
@@ -1729,6 +1729,154 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7.077571156938746e-05</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1762,7 +1910,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1855,7 +2003,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1907,7 +2055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d030/2026-2029.xlsx
+++ b/diseases/d030/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1309,6 +1314,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5514,6 +5524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5662,6 +5677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5810,6 +5830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6733,6 +6758,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9991,6 +10021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13632,6 +13667,11 @@
       <c r="S78" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">

--- a/diseases/d030/2026-2029.xlsx
+++ b/diseases/d030/2026-2029.xlsx
@@ -2172,9 +2172,9 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2184,13 +2184,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2201,6 +2211,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2216,7 +2231,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2298,9 +2317,9 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2310,13 +2329,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2327,6 +2356,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2342,7 +2376,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2424,9 +2462,9 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2436,13 +2474,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2453,6 +2501,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2468,7 +2521,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2550,9 +2607,9 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2562,13 +2619,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2579,6 +2646,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2594,7 +2666,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2676,9 +2752,9 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2688,13 +2764,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2705,6 +2791,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2720,7 +2811,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2802,9 +2897,9 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2814,13 +2909,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2831,6 +2936,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2846,7 +2956,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2928,9 +3042,9 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2940,13 +3054,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -2957,6 +3081,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2972,7 +3101,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
@@ -3054,9 +3187,9 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3066,13 +3199,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3083,6 +3226,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3098,7 +3246,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3180,9 +3332,9 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3192,13 +3344,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3209,6 +3371,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3224,7 +3391,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3306,9 +3477,9 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3318,13 +3489,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3335,6 +3516,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3350,7 +3536,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3432,9 +3622,9 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3444,13 +3634,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3461,6 +3661,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3476,7 +3681,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3558,9 +3767,9 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3570,13 +3779,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3587,6 +3806,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3602,7 +3826,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3684,9 +3912,9 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3696,13 +3924,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3713,6 +3951,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3728,7 +3971,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3810,9 +4057,9 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3822,13 +4069,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -3839,6 +4096,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3854,7 +4116,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3936,9 +4202,9 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3948,13 +4214,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -3965,6 +4241,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3980,7 +4261,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC26" t="inlineStr">
         <is>
           <t>web</t>
@@ -4062,9 +4347,9 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4074,13 +4359,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4091,6 +4386,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4106,7 +4406,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4188,9 +4492,9 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4200,13 +4504,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4217,6 +4531,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4232,7 +4551,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4314,9 +4637,9 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4326,13 +4649,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4343,6 +4676,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4358,7 +4696,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4440,9 +4782,9 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4452,13 +4794,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>all</t>
@@ -4469,6 +4821,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>web</t>
@@ -4484,7 +4841,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC30" t="inlineStr">
         <is>
           <t>web</t>
@@ -4566,9 +4927,9 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4578,13 +4939,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -4595,6 +4966,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>web</t>
@@ -4610,7 +4986,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC31" t="inlineStr">
         <is>
           <t>web</t>
@@ -4692,9 +5072,9 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4704,13 +5084,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -4721,6 +5111,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4736,7 +5131,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4818,9 +5217,9 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4830,13 +5229,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -4847,6 +5256,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4862,7 +5276,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4944,9 +5362,9 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4956,13 +5374,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -4973,6 +5401,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4988,7 +5421,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC34" t="inlineStr">
         <is>
           <t>web</t>
@@ -5070,9 +5507,9 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5082,13 +5519,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5099,6 +5546,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5114,7 +5566,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5196,9 +5652,9 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5208,13 +5664,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5225,6 +5691,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5240,7 +5711,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5322,9 +5797,9 @@
       <c r="R37" t="n">
         <v>0.002165486101390484</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5334,13 +5809,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5351,6 +5836,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5366,7 +5856,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5448,9 +5942,9 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5460,13 +5954,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5477,6 +5981,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5492,7 +6001,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC38" t="inlineStr">
         <is>
           <t>web</t>
